--- a/daily_matches/job_matches_2026-10-10.xlsx
+++ b/daily_matches/job_matches_2026-10-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Development Engineer AI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tampa, FL, USA USA</t>
+          <t>TX, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, MySQL, MongoDB</t>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fb3dc77e214e474</t>
+          <t>https://www.indeed.com/viewjob?jk=0a062edfe43d2da3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer 1 – Finance Technology</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Choice Hotels</t>
+          <t>CLM AI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, Docker, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc62c04cf377635</t>
+          <t>https://www.indeed.com/viewjob?jk=0218b145a5699074</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI &amp; Agentic Architecture</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sony Interactive Entertainment</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, USA USA</t>
+          <t>Tallahassee, FL, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Prompt Engineering, BigQuery, Dataflow, Docker, CI/CD, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,94 +554,94 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaf4f472713024d</t>
+          <t>https://www.indeed.com/viewjob?jk=dceb39b358d3b3f0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AI Engineering – New College Graduate 2027</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Care Access</t>
+          <t>Bitdeer Technologies Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, USA USA</t>
+          <t>San Jose, CA, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, scikit-learn, Athena, Docker, CI/CD, Python</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54af70793b1dd612</t>
+          <t>https://www.indeed.com/viewjob?jk=e296ec36a16413f6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Neural Network Architect</t>
+          <t>Senior Data Scientist - Analytics and Insights Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Precision CastParts</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Rosslyn, VA, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Snowflake, Databricks, Kafka, Python, SQL</t>
+          <t>Data Scientist, RAG, Athena, Data Lake, Apache Airflow, Git, Snowflake, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09d3af3922e9dae</t>
+          <t>https://www.indeed.com/viewjob?jk=18875797ce639c4c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Analytics and Insights Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Baltimore, MD, USA USA</t>
+          <t>Fremont, CA, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Athena, Data Lake, Apache Airflow, Git, Snowflake, Tableau, Power BI, Python</t>
+          <t>LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,24 +659,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9effd1f1f2c8cb44</t>
+          <t>https://www.indeed.com/viewjob?jk=84ff5ba1e8568083</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Senior Security Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, Prompt Engineering, PyTorch, scikit-learn, Docker, Kubernetes, Git, Python</t>
+          <t>Data Scientist, Redshift, Git, Snowflake, Redshift, MySQL, MongoDB, NoSQL, Tableau, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,24 +694,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7eef17f88006caa</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6e777c332d69b7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cypress, CA, USA USA</t>
+          <t>Philadelphia, PA, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,24 +729,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daf104d9c39a6be1</t>
+          <t>https://www.indeed.com/viewjob?jk=5d221c596893433e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, Git, Snowflake, Redshift, MySQL, MongoDB, NoSQL, Tableau, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,24 +764,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e880bd938426b9ef</t>
+          <t>https://www.indeed.com/viewjob?jk=82a2c8d7744d25a8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Data Masking Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bitsight</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -789,17 +789,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, Kubernetes, CI/CD, Git, Hadoop, Python, R, Java</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7060b602cec071b7</t>
+          <t>https://www.indeed.com/viewjob?jk=85220dfd201ee108</t>
         </is>
       </c>
     </row>
@@ -811,20 +811,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>CLM AI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cypress, CA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, RAG, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=328989c1e138152a</t>
+          <t>https://www.indeed.com/viewjob?jk=828decec44fd534b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Analytics Analyst 4 4PC- 890</t>
+          <t>Senior Software Engineer (Data and Embedded SWE)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Olathe, KS, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Databricks, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
+          <t>TensorFlow, PyTorch, scikit-learn, Keras, Git, Polars, Python, R, C++</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,102 +869,102 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73645eb4b3ddaf6e</t>
+          <t>https://www.indeed.com/viewjob?jk=d31f6b6cd341f1fe</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer 2 (Data and Embedded SWE)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Care Access</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, USA USA</t>
+          <t>Olathe, KS, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, scikit-learn, Athena, Redshift, Redshift, Python, SQL, R, Scala</t>
+          <t>PyTorch, scikit-learn, XGBoost, Keras, Git, Polars, Python, R, C++</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572f16346484b378</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab4867ed004a6b1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III – Radiation Effects Tooling</t>
+          <t>Infrastructure Security Engineer (Bare Metal &amp; Platform)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, scikit-learn, Git, Python, SQL, R</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee249cf75376319e</t>
+          <t>https://www.indeed.com/viewjob?jk=a02ba1cc75fa11a7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data &amp; AI Solutions Engineer</t>
+          <t>Specialist, IT App Development</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lisle, IL, USA USA</t>
+          <t>Columbus, OH, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Git, Snowflake, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, C++</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,532 +974,42 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9369214816b39565</t>
+          <t>https://www.indeed.com/viewjob?jk=f6dcdf5a0cf691df</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer Junior</t>
+          <t>Sr. Automation Engineer - IT Asset Management</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Babel</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Jose, CA, USA USA</t>
+          <t>Mountain View, CA, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Data Lake, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>Gemini, Prompt Engineering, Data Lake, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2331dded8b957825</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure &amp; Automation</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>fal - Features &amp; Labels</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, PyTorch, Docker, CI/CD, GitHub Actions, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2072600e04cbc5aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Development Engineer II</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>GM Financial</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Irving, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Generative AI, Copilot, Docker, Kubernetes, Terraform, Git, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9190381fc52ed45c</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior AI Programmer Analyst</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>University of New England</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Portland, ME, USA USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e2707da19a6c0c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Illumina</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>San Diego, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86c732005c445b47</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Data and AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Intermountain Health</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Murray, UT, USA USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, PySpark, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f58b73435c41c623</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Fractal Analytics</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>NJ, USA USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AI Engineer, Copilot, S3, CI/CD, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb715ed4f9bf1243</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>AI Automation Developer II</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Yale New Haven Health</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Stratford, CT, USA USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d38124d843af8bd5</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer- Remote</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Harbor Freight Tools</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Calabasas, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, CI/CD, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=005ad75e75546355</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Software Engineer, Applied Machine Learning</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>fal - Features &amp; Labels</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, Hugging Face, PyTorch, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a86d4dfb173a6f58</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Associated Electric Cooperative Inc</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Springfield, MO, USA USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Data Lake, Git, Databricks, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2aef0cd6e8ac71d</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>RELX Group</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Irving, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Pinecone, Docker, Kubernetes, Terraform, NoSQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b7f8a10a11e2ec2d</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Business Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>State of Wisconsin Investment Board</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Madison, WI, USA USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, CI/CD, Snowflake, Power BI, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=59f3167b2f7e655e</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Infrastructure Security Engineer (Bare Metal &amp; Platform)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>SpaceXAI</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Washington, DC, USA USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=566f188b52aed2c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Swift Solar</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>San Carlos, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Python, SQL, R, Java, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3462c928582ed00a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d274cabb09afe46</t>
         </is>
       </c>
     </row>
